--- a/Output/logit_triple_differences_key_coefficients.xlsx
+++ b/Output/logit_triple_differences_key_coefficients.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">Yes</t>
   </si>
   <si>
-    <t xml:space="preserve">1.161 (0.288)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.216 (0.216)</t>
+    <t xml:space="preserve">1.204 (0.296)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.189* (0.187)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_mean_educ</t>
@@ -59,10 +59,10 @@
     <t xml:space="preserve">0.571 (0.425)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.758 (0.143)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.690 (0.506)</t>
+    <t xml:space="preserve">0.803 (0.165)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.562 (0.446)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_mean_izq_der</t>
@@ -74,10 +74,10 @@
     <t xml:space="preserve">2.377 (4.915)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.914 (0.816)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551 (1.742)</t>
+    <t xml:space="preserve">0.959 (0.796)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.072 (2.864)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_share_desempleado</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">0.002 (0.064)</t>
   </si>
   <si>
-    <t xml:space="preserve">280139698.824* (2878624585.525)</t>
+    <t xml:space="preserve">94287654.610* (920643535.383)</t>
   </si>
   <si>
     <t xml:space="preserve">0.000 (0.000)</t>
@@ -104,10 +104,10 @@
     <t xml:space="preserve">19478956.538** (161221284.367)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.003** (0.007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">446976237.338** (4265107157.911)</t>
+    <t xml:space="preserve">0.002*** (0.005)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2835568724.976** (27295441625.719)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_share_hombre</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">2937997.933 (39545145.784)</t>
   </si>
   <si>
-    <t xml:space="preserve">49719052537.303 (937116222824.308)</t>
+    <t xml:space="preserve">36726909052370.477 (725498170183474.875)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_share_interes_pol_mucho</t>
@@ -125,27 +125,12 @@
     <t xml:space="preserve">0.028 (0.093)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.007 (0.024)</t>
+    <t xml:space="preserve">0.021 (0.075)</t>
   </si>
   <si>
     <t xml:space="preserve">0.000* (0.000)</t>
   </si>
   <si>
-    <t xml:space="preserve">mun_pre_all_share_rural</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551 (0.257)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">241.420*** (458.341)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428* (0.213)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1216.558*** (2386.700)</t>
-  </si>
-  <si>
     <t xml:space="preserve">mun_pre_all_share_voto_blanco_nulo</t>
   </si>
   <si>
@@ -155,10 +140,25 @@
     <t xml:space="preserve">5745262.054 (184919817.641)</t>
   </si>
   <si>
-    <t xml:space="preserve">12.178 (105.860)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24231.669 (861701.481)</t>
+    <t xml:space="preserve">8.536 (71.770)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">226459.367 (7503912.515)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">popdensgeo2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.021 (0.076)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.767 (0.193)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994 (0.095)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772 (0.259)</t>
   </si>
 </sst>
 </file>
@@ -790,7 +790,7 @@
         <v>46</v>
       </c>
       <c r="E18" t="n">
-        <v>7467</v>
+        <v>7503</v>
       </c>
     </row>
     <row r="19">
